--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_valparaiso.xlsx
@@ -135,18 +135,18 @@
     <t xml:space="preserve">El Quisco</t>
   </si>
   <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Cruz</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rinconada</t>
   </si>
   <si>
-    <t xml:space="preserve">Villa Alemana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Cruz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:14</t>
+    <t xml:space="preserve">2026-09-10 00:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1164,7 +1164,7 @@
         <v>39</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
@@ -1203,7 +1203,7 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5304</v>
+        <v>5303</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>

--- a/output/graficos_dimensiones/comunal_e_prebrut_a_2020_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_e_prebrut_a_2020_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:18</t>
+    <t xml:space="preserve">2026-09-18 10:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
